--- a/ch_06/ch_06_solution.xlsx
+++ b/ch_06/ch_06_solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5989BE5A-4300-4A69-9185-F8A8BE142785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBA9B03-0949-4F0A-82CE-06B265196FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -375,10 +375,10 @@
       <xdr:rowOff>101599</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>948956</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>135466</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>573176</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1162843</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -406,8 +406,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="647701" y="1193799"/>
-          <a:ext cx="3294222" cy="2218267"/>
+          <a:off x="3266547" y="1196974"/>
+          <a:ext cx="4517848" cy="3069432"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -421,13 +421,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>736600</xdr:colOff>
       <xdr:row>99</xdr:row>
-      <xdr:rowOff>148166</xdr:rowOff>
+      <xdr:rowOff>148165</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>11727</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>829469</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>145441</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -455,8 +455,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="736600" y="14346766"/>
-          <a:ext cx="3119967" cy="3140161"/>
+          <a:off x="736600" y="19341040"/>
+          <a:ext cx="4664869" cy="4743901"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8986,6 +8986,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
+    <row r="18" spans="1:7" ht="102.4" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="str" cm="1">
         <f t="array" ref="A23:C28">_xlfn._xlws.PY(2,0)</f>
